--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6573,9 +6573,17 @@
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="2">
         <f>VLOOKUP($A33,Fixture!$A:$F,5,0)</f>
@@ -6790,9 +6798,17 @@
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="2">
         <f>VLOOKUP($A42,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6823,9 +6823,17 @@
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="B43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="2">
         <f>VLOOKUP($A43,Fixture!$A:$F,5,0)</f>
@@ -6840,9 +6848,17 @@
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
+      <c r="B44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="2">
         <f>VLOOKUP($A44,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6873,9 +6873,17 @@
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="B45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="2">
         <f>VLOOKUP($A45,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6898,9 +6898,17 @@
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
+      <c r="B46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="2">
         <f>VLOOKUP($A46,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6923,9 +6923,17 @@
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="2">
         <f>VLOOKUP($A47,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6948,9 +6948,17 @@
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="2">
         <f>VLOOKUP($A48,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6973,9 +6973,17 @@
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
+      <c r="B49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="2">
         <f>VLOOKUP($A49,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -6998,9 +6998,17 @@
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
+      <c r="B50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="2">
         <f>VLOOKUP($A50,Fixture!$A:$F,5,0)</f>
@@ -7015,9 +7023,17 @@
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+      <c r="B51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="2">
         <f>VLOOKUP($A51,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7048,9 +7048,17 @@
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="2">
         <f>VLOOKUP($A52,Fixture!$A:$F,5,0)</f>
@@ -7065,9 +7073,17 @@
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
+      <c r="B53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="2">
         <f>VLOOKUP($A53,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7098,9 +7098,17 @@
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="2">
         <f>VLOOKUP($A54,Fixture!$A:$F,5,0)</f>
@@ -7115,9 +7123,17 @@
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
+      <c r="B55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="2">
         <f>VLOOKUP($A55,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7148,9 +7148,17 @@
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="2">
         <f>VLOOKUP($A56,Fixture!$A:$F,5,0)</f>
@@ -7165,9 +7173,17 @@
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
+      <c r="B57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="2">
         <f>VLOOKUP($A57,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7198,9 +7198,17 @@
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
+      <c r="B58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="2">
         <f>VLOOKUP($A58,Fixture!$A:$F,5,0)</f>
@@ -7215,9 +7223,17 @@
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
+      <c r="B59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="2">
         <f>VLOOKUP($A59,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7248,9 +7248,17 @@
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
+      <c r="B60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="2">
         <f>VLOOKUP($A60,Fixture!$A:$F,5,0)</f>
@@ -7265,9 +7273,17 @@
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="2">
         <f>VLOOKUP($A61,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7298,9 +7298,17 @@
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
+      <c r="B62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="2">
         <f>VLOOKUP($A62,Fixture!$A:$F,5,0)</f>
@@ -7315,9 +7323,17 @@
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
+      <c r="B63" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="2">
         <f>VLOOKUP($A63,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7348,9 +7348,17 @@
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="2">
         <f>VLOOKUP($A64,Fixture!$A:$F,5,0)</f>
@@ -7365,9 +7373,17 @@
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="2">
         <f>VLOOKUP($A65,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7398,9 +7398,17 @@
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
+      <c r="B66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="2">
         <f>VLOOKUP($A66,Fixture!$A:$F,5,0)</f>
@@ -7415,9 +7423,17 @@
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
+      <c r="B67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="2">
         <f>VLOOKUP($A67,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7448,9 +7448,17 @@
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
+      <c r="B68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="2">
         <f>VLOOKUP($A68,Fixture!$A:$F,5,0)</f>
@@ -7465,9 +7473,17 @@
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
+      <c r="B69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="2">
         <f>VLOOKUP($A69,Fixture!$A:$F,5,0)</f>
@@ -7482,9 +7498,17 @@
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="2">
         <f>VLOOKUP($A70,Fixture!$A:$F,5,0)</f>
@@ -7499,9 +7523,17 @@
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
+      <c r="B71" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="2">
         <f>VLOOKUP($A71,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7548,9 +7548,17 @@
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
+      <c r="B72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="2">
         <f>VLOOKUP($A72,Fixture!$A:$F,5,0)</f>
@@ -7565,9 +7573,17 @@
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
+      <c r="B73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="2">
         <f>VLOOKUP($A73,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7598,9 +7598,17 @@
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="2">
         <f>VLOOKUP($A74,Fixture!$A:$F,5,0)</f>
@@ -7615,9 +7623,17 @@
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
+      <c r="B75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="2">
         <f>VLOOKUP($A75,Fixture!$A:$F,5,0)</f>
@@ -7632,43 +7648,71 @@
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="2">
-        <f>VLOOKUP($A76,Fixture!$A:$F,5,0)</f>
-        <v/>
-      </c>
-      <c r="G76" s="2">
-        <f>VLOOKUP($A76,Fixture!$A:$F,6,0)</f>
-        <v/>
+      <c r="B76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="2">
-        <f>VLOOKUP($A77,Fixture!$A:$F,5,0)</f>
-        <v/>
-      </c>
-      <c r="G77" s="2">
-        <f>VLOOKUP($A77,Fixture!$A:$F,6,0)</f>
-        <v/>
+      <c r="B77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Marruecos</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
+      <c r="B78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="2">
         <f>VLOOKUP($A78,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7727,9 +7727,17 @@
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
+      <c r="B79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="2">
         <f>VLOOKUP($A79,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7752,9 +7752,17 @@
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
+      <c r="B80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="2">
         <f>VLOOKUP($A80,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7777,9 +7777,17 @@
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
+      <c r="B81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="2">
         <f>VLOOKUP($A81,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7802,9 +7802,17 @@
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
+      <c r="B82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="2">
         <f>VLOOKUP($A82,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7827,9 +7827,17 @@
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
+      <c r="B83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E83" s="3" t="n"/>
       <c r="F83" s="2">
         <f>VLOOKUP($A83,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7852,9 +7852,17 @@
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
+      <c r="B84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="2">
         <f>VLOOKUP($A84,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7877,9 +7877,17 @@
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
+      <c r="B85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="2">
         <f>VLOOKUP($A85,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7902,9 +7902,17 @@
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
+      <c r="B86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="2">
         <f>VLOOKUP($A86,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7927,17 +7927,27 @@
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="2">
-        <f>VLOOKUP($A87,Fixture!$A:$F,5,0)</f>
-        <v/>
-      </c>
-      <c r="G87" s="2">
-        <f>VLOOKUP($A87,Fixture!$A:$F,6,0)</f>
-        <v/>
+      <c r="B87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Egipto</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -7954,9 +7954,17 @@
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
+      <c r="B88" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="2">
         <f>VLOOKUP($A88,Fixture!$A:$F,5,0)</f>
@@ -7971,9 +7979,17 @@
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
+      <c r="B89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E89" s="3" t="n"/>
       <c r="F89" s="2">
         <f>VLOOKUP($A89,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -8004,9 +8004,17 @@
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
+      <c r="B90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="2">
         <f>VLOOKUP($A90,Fixture!$A:$F,5,0)</f>
@@ -8021,9 +8029,17 @@
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="3" t="n"/>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
+      <c r="B91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="2">
         <f>VLOOKUP($A91,Fixture!$A:$F,5,0)</f>
@@ -8038,9 +8054,17 @@
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="2">
         <f>VLOOKUP($A92,Fixture!$A:$F,5,0)</f>
@@ -8055,9 +8079,17 @@
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="3" t="n"/>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
+      <c r="B93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="2">
         <f>VLOOKUP($A93,Fixture!$A:$F,5,0)</f>
@@ -8072,9 +8104,17 @@
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="3" t="n"/>
-      <c r="C94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
+      <c r="B94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="2">
         <f>VLOOKUP($A94,Fixture!$A:$F,5,0)</f>
@@ -8089,9 +8129,17 @@
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="3" t="n"/>
-      <c r="C95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
+      <c r="B95" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="2">
         <f>VLOOKUP($A95,Fixture!$A:$F,5,0)</f>
@@ -8106,9 +8154,17 @@
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="3" t="n"/>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
+      <c r="B96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E96" s="3" t="n"/>
       <c r="F96" s="2">
         <f>VLOOKUP($A96,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5271,12 +5271,12 @@
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>W86</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>W88</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -5319,12 +5319,12 @@
       <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>W85</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>W87</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -5367,12 +5367,12 @@
       <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>W89</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>W90</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -5415,12 +5415,12 @@
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>W93</t>
+          <t>España</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>W94</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -5463,12 +5463,12 @@
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>W91</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>W92</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -5511,7 +5511,7 @@
       <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>W95</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>W96</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -8179,17 +8179,27 @@
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="3" t="n"/>
-      <c r="C97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="2">
-        <f>VLOOKUP($A97,Fixture!$A:$F,5,0)</f>
-        <v/>
-      </c>
-      <c r="G97" s="2">
-        <f>VLOOKUP($A97,Fixture!$A:$F,6,0)</f>
-        <v/>
+      <c r="B97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Suiza</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5559,7 +5559,7 @@
       <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>W97</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -8206,9 +8206,17 @@
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="3" t="n"/>
-      <c r="C98" s="3" t="n"/>
-      <c r="D98" s="3" t="n"/>
+      <c r="B98" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E98" s="3" t="n"/>
       <c r="F98" s="2">
         <f>VLOOKUP($A98,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5564,7 +5564,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>W98</t>
+          <t>España</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -8231,9 +8231,17 @@
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="n"/>
-      <c r="C99" s="3" t="n"/>
-      <c r="D99" s="3" t="n"/>
+      <c r="B99" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E99" s="3" t="n"/>
       <c r="F99" s="2">
         <f>VLOOKUP($A99,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5607,7 +5607,7 @@
       <c r="D103" s="2" t="n"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>W99</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -8256,9 +8256,17 @@
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="3" t="n"/>
-      <c r="C100" s="3" t="n"/>
-      <c r="D100" s="3" t="n"/>
+      <c r="B100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
       <c r="E100" s="3" t="n"/>
       <c r="F100" s="2">
         <f>VLOOKUP($A100,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5612,7 +5612,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>W100</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -8281,9 +8281,17 @@
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="n"/>
-      <c r="C101" s="3" t="n"/>
-      <c r="D101" s="3" t="n"/>
+      <c r="B101" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
       <c r="E101" s="3" t="n"/>
       <c r="F101" s="2">
         <f>VLOOKUP($A101,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -8306,9 +8306,17 @@
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="3" t="n"/>
-      <c r="D102" s="3" t="n"/>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E102" s="3" t="n"/>
       <c r="F102" s="2">
         <f>VLOOKUP($A102,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5655,7 +5655,7 @@
       <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       <c r="D105" s="2" t="n"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>W101</t>
+          <t>España</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>W102</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -8331,9 +8331,17 @@
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="3" t="n"/>
-      <c r="C103" s="3" t="n"/>
-      <c r="D103" s="3" t="n"/>
+      <c r="B103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E103" s="3" t="n"/>
       <c r="F103" s="2">
         <f>VLOOKUP($A103,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -8356,9 +8356,17 @@
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="3" t="n"/>
-      <c r="C104" s="3" t="n"/>
-      <c r="D104" s="3" t="n"/>
+      <c r="B104" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="E104" s="3" t="n"/>
       <c r="F104" s="2">
         <f>VLOOKUP($A104,Fixture!$A:$F,5,0)</f>

--- a/output/Mundial2026_Tracker.xlsx
+++ b/output/Mundial2026_Tracker.xlsx
@@ -8381,9 +8381,17 @@
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="3" t="n"/>
-      <c r="C105" s="3" t="n"/>
-      <c r="D105" s="3" t="n"/>
+      <c r="B105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
       <c r="E105" s="3" t="n"/>
       <c r="F105" s="2">
         <f>VLOOKUP($A105,Fixture!$A:$F,5,0)</f>
